--- a/data/processed_data/20V_1/contracciones_20V_1.xlsx
+++ b/data/processed_data/20V_1/contracciones_20V_1.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:BN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,6 +1052,71 @@
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
+          <t>forzada_cinetica_n_pulsos</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_n_con_cruce</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_reportable</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_ms</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_ic95_ms</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_ttp_cota_ms</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_n_con_cruce</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_reportable</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_ms</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_ic95_ms</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>forzada_rt50_cota_ms</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
           <t>forzada_periodo_origen</t>
         </is>
       </c>
@@ -1223,7 +1288,50 @@
       <c r="AZ2" t="n">
         <v>0.08407780782078697</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>173.7243302182036</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>157-184</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>249.9999999999858</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>166.813264411639</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>167-179</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>233.3333333333201</v>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>1/0.1 Hz +-2 %</t>
         </is>
@@ -1240,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1259,6 +1367,36 @@
           <t>responde</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_ms</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_ms</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1270,6 +1408,24 @@
       <c r="C2" t="b">
         <v>1</v>
       </c>
+      <c r="D2" t="n">
+        <v>183.6224550742099</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>299.9999999999829</v>
+      </c>
+      <c r="G2" t="n">
+        <v>166.8052984866165</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>266.6666666666515</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1281,6 +1437,24 @@
       <c r="C3" t="b">
         <v>1</v>
       </c>
+      <c r="D3" t="n">
+        <v>173.7243302182036</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>266.6666666666515</v>
+      </c>
+      <c r="G3" t="n">
+        <v>179.4262488627764</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>233.3333333333201</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1292,6 +1466,24 @@
       <c r="C4" t="b">
         <v>1</v>
       </c>
+      <c r="D4" t="n">
+        <v>94.54496222487063</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>233.3333333333201</v>
+      </c>
+      <c r="G4" t="n">
+        <v>120.2075397666953</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>233.3333333333201</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1303,6 +1495,24 @@
       <c r="C5" t="b">
         <v>1</v>
       </c>
+      <c r="D5" t="n">
+        <v>157.0273129608335</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>199.9999999999886</v>
+      </c>
+      <c r="G5" t="n">
+        <v>130.7324651284819</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>166.6666666666572</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1314,6 +1524,24 @@
       <c r="C6" t="b">
         <v>1</v>
       </c>
+      <c r="D6" t="n">
+        <v>180.5969049497904</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>233.3333333333201</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25.90752212619383</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>66.66666666666288</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1552,24 @@
       </c>
       <c r="C7" t="b">
         <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>170.9049337286015</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>266.6666666666515</v>
+      </c>
+      <c r="G7" t="n">
+        <v>166.813264411639</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>299.9999999999829</v>
       </c>
     </row>
   </sheetData>
